--- a/z0bug_odoo/z0bug_odoo/data/account_fiscal_position.xlsx
+++ b/z0bug_odoo/z0bug_odoo/data/account_fiscal_position.xlsx
@@ -8,7 +8,7 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="account_fiscal_position" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="account_fiscal_position" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="96">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -58,6 +58,15 @@
     <t xml:space="preserve">self_journal_id</t>
   </si>
   <si>
+    <t xml:space="preserve">payment_journal_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">transient_account_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rc_fiscal_document_type_id</t>
+  </si>
+  <si>
     <t xml:space="preserve">z0bug.fiscalpos_it</t>
   </si>
   <si>
@@ -76,19 +85,34 @@
     <t xml:space="preserve">l10n_it_reverse_charge.account_rc_type_3</t>
   </si>
   <si>
+    <t xml:space="preserve">supplier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">external.ARC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">external.GC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">external.490050</t>
+  </si>
+  <si>
+    <t xml:space="preserve">external.TD18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">z0bug.fiscalpos_xx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regime Extra comunitario</t>
+  </si>
+  <si>
+    <t xml:space="preserve">l10n_it_reverse_charge.account_rc_type_2</t>
+  </si>
+  <si>
     <t xml:space="preserve">other</t>
   </si>
   <si>
-    <t xml:space="preserve">external.ARC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">z0bug.fiscalpos_xx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regime Extra comunitario</t>
-  </si>
-  <si>
-    <t xml:space="preserve">l10n_it_reverse_charge.account_rc_type_2</t>
+    <t xml:space="preserve">external.TD17</t>
   </si>
   <si>
     <t xml:space="preserve">z0bug.fiscalpos_rc</t>
@@ -100,10 +124,10 @@
     <t xml:space="preserve">Reverse charge locale</t>
   </si>
   <si>
-    <t xml:space="preserve">local</t>
-  </si>
-  <si>
     <t xml:space="preserve">l10n_it_reverse_charge.account_rc_type_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">external.TD19</t>
   </si>
   <si>
     <t xml:space="preserve">z0bug.fiscalpos_sp</t>
@@ -316,9 +340,9 @@
       <family val="0"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
@@ -365,12 +389,16 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -386,560 +414,714 @@
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
+  <a:themeElements>
+    <a:clrScheme name="LibreOffice">
+      <a:dk1>
+        <a:srgbClr val="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:srgbClr val="ffffff"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="000000"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="ffffff"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="18a303"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="0369a3"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="a33e03"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8e03a3"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="c99c00"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="c9211e"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000ee"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="551a8b"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme>
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L34"/>
+  <dimension ref="A1:O34"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="17.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="44.6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="9.35"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="25.06"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="11.3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="8.1"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="26.32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="36.03"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="13.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="17.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="44.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="9.35"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="25.04"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="10.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="12.51"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="8.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="26.32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="6.96"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="36.03"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="11.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="13.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="18.64"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="19.93"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="23.41"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="16" style="1" width="11.72"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="0" t="s">
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="0" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="0" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="0" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="0" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="C2" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="D2" s="0" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="0" t="n">
-        <v>8</v>
-      </c>
-      <c r="D3" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" s="0" t="s">
+      <c r="D4" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="J3" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="K3" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="L3" s="1" t="s">
+      <c r="D5" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I5" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="J5" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="C4" s="0" t="n">
-        <v>12</v>
-      </c>
-      <c r="D4" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="G4" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="J4" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="K4" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="B5" s="0" t="s">
+      <c r="D6" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F6" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="C5" s="0" t="n">
-        <v>16</v>
-      </c>
-      <c r="D5" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="I5" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="J5" s="0" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="D7" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H7" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8" s="1" t="n">
         <v>28</v>
       </c>
-      <c r="B6" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="C6" s="0" t="n">
-        <v>20</v>
-      </c>
-      <c r="D6" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="F6" s="0" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="B7" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="C7" s="0" t="n">
-        <v>24</v>
-      </c>
-      <c r="D7" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="H7" s="0" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="C8" s="0" t="n">
-        <v>28</v>
-      </c>
-      <c r="D8" s="0" t="s">
-        <v>35</v>
+      <c r="D8" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="C9" s="0" t="n">
+      <c r="A9" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="D9" s="0" t="s">
-        <v>37</v>
-      </c>
-      <c r="G9" s="0" t="n">
+      <c r="D9" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G9" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
-        <v>38</v>
-      </c>
-      <c r="C10" s="0" t="n">
+      <c r="A10" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C10" s="1" t="n">
         <v>101</v>
       </c>
-      <c r="D10" s="0" t="s">
-        <v>39</v>
-      </c>
-      <c r="G10" s="0" t="n">
+      <c r="D10" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G10" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
-        <v>40</v>
-      </c>
-      <c r="C11" s="0" t="n">
+      <c r="A11" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C11" s="1" t="n">
         <v>102</v>
       </c>
-      <c r="D11" s="0" t="s">
-        <v>41</v>
-      </c>
-      <c r="G11" s="0" t="n">
+      <c r="D11" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="G11" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
-        <v>42</v>
-      </c>
-      <c r="C12" s="0" t="n">
+      <c r="A12" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C12" s="1" t="n">
         <v>103</v>
       </c>
-      <c r="D12" s="0" t="s">
-        <v>43</v>
-      </c>
-      <c r="G12" s="0" t="n">
+      <c r="D12" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="G12" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
-        <v>44</v>
-      </c>
-      <c r="C13" s="0" t="n">
+      <c r="A13" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C13" s="1" t="n">
         <v>104</v>
       </c>
-      <c r="D13" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="G13" s="0" t="n">
+      <c r="D13" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="G13" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
-        <v>46</v>
-      </c>
-      <c r="C14" s="0" t="n">
+      <c r="A14" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C14" s="1" t="n">
         <v>105</v>
       </c>
-      <c r="D14" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="G14" s="0" t="n">
+      <c r="D14" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="G14" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="C15" s="0" t="n">
+      <c r="A15" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C15" s="1" t="n">
         <v>106</v>
       </c>
-      <c r="D15" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="G15" s="0" t="n">
+      <c r="D15" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G15" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="C16" s="0" t="n">
+      <c r="A16" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C16" s="1" t="n">
         <v>107</v>
       </c>
-      <c r="D16" s="0" t="s">
-        <v>51</v>
-      </c>
-      <c r="G16" s="0" t="n">
+      <c r="D16" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="G16" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
-        <v>52</v>
-      </c>
-      <c r="C17" s="0" t="n">
+      <c r="A17" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C17" s="1" t="n">
         <v>108</v>
       </c>
-      <c r="D17" s="0" t="s">
-        <v>53</v>
-      </c>
-      <c r="G17" s="0" t="n">
+      <c r="D17" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G17" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
-        <v>54</v>
-      </c>
-      <c r="C18" s="0" t="n">
+      <c r="A18" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C18" s="1" t="n">
         <v>109</v>
       </c>
-      <c r="D18" s="0" t="s">
-        <v>55</v>
-      </c>
-      <c r="G18" s="0" t="n">
+      <c r="D18" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="G18" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
-        <v>56</v>
-      </c>
-      <c r="C19" s="0" t="n">
+      <c r="A19" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C19" s="1" t="n">
         <v>110</v>
       </c>
-      <c r="D19" s="0" t="s">
-        <v>57</v>
-      </c>
-      <c r="G19" s="0" t="n">
+      <c r="D19" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="G19" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
-        <v>58</v>
-      </c>
-      <c r="C20" s="0" t="n">
+      <c r="A20" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C20" s="1" t="n">
         <v>111</v>
       </c>
-      <c r="D20" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="G20" s="0" t="n">
+      <c r="D20" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="G20" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
-        <v>60</v>
-      </c>
-      <c r="C21" s="0" t="n">
+      <c r="A21" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C21" s="1" t="n">
         <v>112</v>
       </c>
-      <c r="D21" s="0" t="s">
-        <v>61</v>
-      </c>
-      <c r="G21" s="0" t="n">
+      <c r="D21" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G21" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
-        <v>62</v>
-      </c>
-      <c r="C22" s="0" t="n">
+      <c r="A22" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C22" s="1" t="n">
         <v>113</v>
       </c>
-      <c r="D22" s="0" t="s">
-        <v>63</v>
-      </c>
-      <c r="G22" s="0" t="n">
+      <c r="D22" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G22" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
-        <v>64</v>
-      </c>
-      <c r="C23" s="0" t="n">
+      <c r="A23" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C23" s="1" t="n">
         <v>114</v>
       </c>
-      <c r="D23" s="0" t="s">
-        <v>65</v>
-      </c>
-      <c r="G23" s="0" t="n">
+      <c r="D23" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G23" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
-        <v>66</v>
-      </c>
-      <c r="C24" s="0" t="n">
+      <c r="A24" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C24" s="1" t="n">
         <v>115</v>
       </c>
-      <c r="D24" s="0" t="s">
-        <v>67</v>
-      </c>
-      <c r="G24" s="0" t="n">
+      <c r="D24" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="G24" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
-        <v>68</v>
-      </c>
-      <c r="C25" s="0" t="n">
+      <c r="A25" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C25" s="1" t="n">
         <v>116</v>
       </c>
-      <c r="D25" s="0" t="s">
-        <v>69</v>
-      </c>
-      <c r="G25" s="0" t="n">
+      <c r="D25" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G25" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
-        <v>70</v>
-      </c>
-      <c r="C26" s="0" t="n">
+      <c r="A26" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C26" s="1" t="n">
         <v>117</v>
       </c>
-      <c r="D26" s="0" t="s">
-        <v>71</v>
-      </c>
-      <c r="G26" s="0" t="n">
+      <c r="D26" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="G26" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
-        <v>72</v>
-      </c>
-      <c r="C27" s="0" t="n">
+      <c r="A27" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C27" s="1" t="n">
         <v>118</v>
       </c>
-      <c r="D27" s="0" t="s">
-        <v>73</v>
-      </c>
-      <c r="G27" s="0" t="n">
+      <c r="D27" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="G27" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="s">
-        <v>74</v>
-      </c>
-      <c r="C28" s="0" t="n">
+      <c r="A28" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C28" s="1" t="n">
         <v>119</v>
       </c>
-      <c r="D28" s="0" t="s">
-        <v>75</v>
-      </c>
-      <c r="G28" s="0" t="n">
+      <c r="D28" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="G28" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="s">
-        <v>76</v>
-      </c>
-      <c r="C29" s="0" t="n">
+      <c r="A29" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C29" s="1" t="n">
         <v>120</v>
       </c>
-      <c r="D29" s="0" t="s">
-        <v>77</v>
-      </c>
-      <c r="G29" s="0" t="n">
+      <c r="D29" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="G29" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="s">
-        <v>78</v>
-      </c>
-      <c r="C30" s="0" t="n">
+      <c r="A30" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C30" s="1" t="n">
         <v>121</v>
       </c>
-      <c r="D30" s="0" t="s">
-        <v>79</v>
-      </c>
-      <c r="G30" s="0" t="n">
+      <c r="D30" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="G30" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0" t="s">
-        <v>80</v>
-      </c>
-      <c r="C31" s="0" t="n">
+      <c r="A31" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C31" s="1" t="n">
         <v>122</v>
       </c>
-      <c r="D31" s="0" t="s">
-        <v>81</v>
-      </c>
-      <c r="G31" s="0" t="n">
+      <c r="D31" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="G31" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0" t="s">
-        <v>82</v>
-      </c>
-      <c r="C32" s="0" t="n">
+      <c r="A32" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C32" s="1" t="n">
         <v>123</v>
       </c>
-      <c r="D32" s="0" t="s">
-        <v>83</v>
-      </c>
-      <c r="G32" s="0" t="n">
+      <c r="D32" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="G32" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="0" t="s">
-        <v>84</v>
-      </c>
-      <c r="C33" s="0" t="n">
+      <c r="A33" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C33" s="1" t="n">
         <v>124</v>
       </c>
-      <c r="D33" s="0" t="s">
-        <v>85</v>
-      </c>
-      <c r="G33" s="0" t="n">
+      <c r="D33" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="G33" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="0" t="s">
-        <v>86</v>
-      </c>
-      <c r="C34" s="0" t="n">
+      <c r="A34" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C34" s="1" t="n">
         <v>125</v>
       </c>
-      <c r="D34" s="0" t="s">
-        <v>87</v>
-      </c>
-      <c r="G34" s="0" t="n">
+      <c r="D34" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="G34" s="1" t="n">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,Normale"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Normale"&amp;12Pagina &amp;P</oddFooter>
